--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/132.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/132.xlsx
@@ -426,13 +426,13 @@
         <v>-0.5872775316781849</v>
       </c>
       <c r="E2">
-        <v>-22.09725905915095</v>
+        <v>-20.28118434314317</v>
       </c>
       <c r="F2">
-        <v>-4.224532250699108</v>
+        <v>-4.95266636939247</v>
       </c>
       <c r="G2">
-        <v>-11.27029145227277</v>
+        <v>-12.23704234212824</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.1558594739875458</v>
       </c>
       <c r="E3">
-        <v>-22.84640285828955</v>
+        <v>-20.00973875737503</v>
       </c>
       <c r="F3">
-        <v>-4.473102113991961</v>
+        <v>-5.036327335238206</v>
       </c>
       <c r="G3">
-        <v>-12.33348846881315</v>
+        <v>-11.30375858718625</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.2695895409019458</v>
       </c>
       <c r="E4">
-        <v>-21.77013136915083</v>
+        <v>-20.81998875473583</v>
       </c>
       <c r="F4">
-        <v>-3.665536673411557</v>
+        <v>-4.549545514657105</v>
       </c>
       <c r="G4">
-        <v>-11.6035764960297</v>
+        <v>-11.11488296436986</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.6441555517876248</v>
       </c>
       <c r="E5">
-        <v>-22.33005486033024</v>
+        <v>-20.60633095134135</v>
       </c>
       <c r="F5">
-        <v>-4.335800216977943</v>
+        <v>-4.605581255986881</v>
       </c>
       <c r="G5">
-        <v>-11.20223717301622</v>
+        <v>-10.50760419189248</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.9732993307455036</v>
       </c>
       <c r="E6">
-        <v>-24.07784662894651</v>
+        <v>-22.20275893322424</v>
       </c>
       <c r="F6">
-        <v>-4.899787536234764</v>
+        <v>-4.8187516666885</v>
       </c>
       <c r="G6">
-        <v>-11.741417283579</v>
+        <v>-11.04043236086508</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.254714749042853</v>
       </c>
       <c r="E7">
-        <v>-23.30162804518135</v>
+        <v>-23.15431363948969</v>
       </c>
       <c r="F7">
-        <v>-5.052195541206234</v>
+        <v>-4.287294335339615</v>
       </c>
       <c r="G7">
-        <v>-10.70117915497287</v>
+        <v>-11.10719171080444</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.496292235258186</v>
       </c>
       <c r="E8">
-        <v>-24.87106845987551</v>
+        <v>-22.64413731355907</v>
       </c>
       <c r="F8">
-        <v>-5.154159284816825</v>
+        <v>-4.289504419570284</v>
       </c>
       <c r="G8">
-        <v>-11.52424641088413</v>
+        <v>-10.08632008557519</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.705417251125577</v>
       </c>
       <c r="E9">
-        <v>-24.15212681349107</v>
+        <v>-23.26046556774098</v>
       </c>
       <c r="F9">
-        <v>-3.97808549305963</v>
+        <v>-4.325999802235422</v>
       </c>
       <c r="G9">
-        <v>-9.875998501315102</v>
+        <v>-10.64627258547717</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>1.894528608865129</v>
       </c>
       <c r="E10">
-        <v>-24.73965670034661</v>
+        <v>-24.99473863349493</v>
       </c>
       <c r="F10">
-        <v>-4.112199832307675</v>
+        <v>-3.881237746528728</v>
       </c>
       <c r="G10">
-        <v>-10.85121734125185</v>
+        <v>-9.940746272547006</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.070193244291868</v>
       </c>
       <c r="E11">
-        <v>-24.20191551085311</v>
+        <v>-24.68306088962317</v>
       </c>
       <c r="F11">
-        <v>-4.447327462253854</v>
+        <v>-4.053800758777713</v>
       </c>
       <c r="G11">
-        <v>-9.873238944282294</v>
+        <v>-9.589030677349111</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.244798552650672</v>
       </c>
       <c r="E12">
-        <v>-28.31498189501586</v>
+        <v>-25.66425291190259</v>
       </c>
       <c r="F12">
-        <v>-4.102059786930006</v>
+        <v>-3.959030557693032</v>
       </c>
       <c r="G12">
-        <v>-9.346569521800125</v>
+        <v>-9.229102985039869</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.424050811599532</v>
       </c>
       <c r="E13">
-        <v>-29.07900872693698</v>
+        <v>-25.89061954195105</v>
       </c>
       <c r="F13">
-        <v>-4.062846530816284</v>
+        <v>-3.80035181148237</v>
       </c>
       <c r="G13">
-        <v>-9.411797670036794</v>
+        <v>-8.996194543949766</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.614773364205841</v>
       </c>
       <c r="E14">
-        <v>-27.44883797964552</v>
+        <v>-26.9532975704236</v>
       </c>
       <c r="F14">
-        <v>-3.968848368151012</v>
+        <v>-3.576461498221123</v>
       </c>
       <c r="G14">
-        <v>-9.312162518833842</v>
+        <v>-8.251272095139708</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.819295285617424</v>
       </c>
       <c r="E15">
-        <v>-30.22972860567891</v>
+        <v>-28.07728115126195</v>
       </c>
       <c r="F15">
-        <v>-4.043924962601537</v>
+        <v>-3.450673908106018</v>
       </c>
       <c r="G15">
-        <v>-8.60341454707825</v>
+        <v>-7.464456333248351</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.032278366794132</v>
       </c>
       <c r="E16">
-        <v>-28.86187676226928</v>
+        <v>-28.62529738557307</v>
       </c>
       <c r="F16">
-        <v>-3.607579119707286</v>
+        <v>-3.342974548598443</v>
       </c>
       <c r="G16">
-        <v>-9.110511217360845</v>
+        <v>-8.02448193399888</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.247578354889654</v>
       </c>
       <c r="E17">
-        <v>-30.09004780240228</v>
+        <v>-29.61300579642115</v>
       </c>
       <c r="F17">
-        <v>-3.288130827961296</v>
+        <v>-3.189745631530799</v>
       </c>
       <c r="G17">
-        <v>-7.370401648608904</v>
+        <v>-6.724263248265094</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.449176831414237</v>
       </c>
       <c r="E18">
-        <v>-31.69919499396746</v>
+        <v>-30.66339031937221</v>
       </c>
       <c r="F18">
-        <v>-3.311159441759123</v>
+        <v>-2.770655510004265</v>
       </c>
       <c r="G18">
-        <v>-7.15284046959766</v>
+        <v>-6.218971907867255</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.622732034306955</v>
       </c>
       <c r="E19">
-        <v>-32.48492027845515</v>
+        <v>-31.53729243349733</v>
       </c>
       <c r="F19">
-        <v>-2.684832505237222</v>
+        <v>-2.507556910833711</v>
       </c>
       <c r="G19">
-        <v>-6.85864871534806</v>
+        <v>-6.345679175107756</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.752262507258973</v>
       </c>
       <c r="E20">
-        <v>-33.81963364870397</v>
+        <v>-31.76823797903141</v>
       </c>
       <c r="F20">
-        <v>-3.136790588572035</v>
+        <v>-2.220664286385144</v>
       </c>
       <c r="G20">
-        <v>-7.851543601538944</v>
+        <v>-5.693047852965848</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.823096814940607</v>
       </c>
       <c r="E21">
-        <v>-34.43529946567957</v>
+        <v>-32.64001157235256</v>
       </c>
       <c r="F21">
-        <v>-2.58568852426576</v>
+        <v>-1.724612206199313</v>
       </c>
       <c r="G21">
-        <v>-6.593686857540563</v>
+        <v>-6.500431060745997</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.829568779609846</v>
       </c>
       <c r="E22">
-        <v>-34.75254043612093</v>
+        <v>-34.00081956935528</v>
       </c>
       <c r="F22">
-        <v>-1.915404271514304</v>
+        <v>-1.638250762620451</v>
       </c>
       <c r="G22">
-        <v>-6.776347602857804</v>
+        <v>-6.111748627510233</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.767813986143524</v>
       </c>
       <c r="E23">
-        <v>-35.40653831701903</v>
+        <v>-35.30081832274553</v>
       </c>
       <c r="F23">
-        <v>-2.529149135555083</v>
+        <v>-1.364603732942648</v>
       </c>
       <c r="G23">
-        <v>-7.287116285407798</v>
+        <v>-6.189159815381333</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.64595182390684</v>
       </c>
       <c r="E24">
-        <v>-34.87626252488192</v>
+        <v>-34.92605329884962</v>
       </c>
       <c r="F24">
-        <v>-2.178844986422214</v>
+        <v>-1.246288845168197</v>
       </c>
       <c r="G24">
-        <v>-7.24103925411924</v>
+        <v>-5.786731811873358</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.475247075443171</v>
       </c>
       <c r="E25">
-        <v>-35.64220814043511</v>
+        <v>-34.70783526942048</v>
       </c>
       <c r="F25">
-        <v>-2.384988356445885</v>
+        <v>-1.24139236545025</v>
       </c>
       <c r="G25">
-        <v>-6.459366659072376</v>
+        <v>-6.424855226322449</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.269968071889276</v>
       </c>
       <c r="E26">
-        <v>-33.66759704173597</v>
+        <v>-35.67088814123871</v>
       </c>
       <c r="F26">
-        <v>-2.163737221729956</v>
+        <v>-1.147360239721464</v>
       </c>
       <c r="G26">
-        <v>-6.526504566977445</v>
+        <v>-5.788880454671844</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.050078576763741</v>
       </c>
       <c r="E27">
-        <v>-35.93170150601529</v>
+        <v>-36.01244408738128</v>
       </c>
       <c r="F27">
-        <v>-1.308128956889389</v>
+        <v>-1.125462347428459</v>
       </c>
       <c r="G27">
-        <v>-6.746279657401953</v>
+        <v>-6.491014105005851</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.828874334436804</v>
       </c>
       <c r="E28">
-        <v>-36.28485529478245</v>
+        <v>-36.34860916522423</v>
       </c>
       <c r="F28">
-        <v>-1.537874999321026</v>
+        <v>-1.308765143054739</v>
       </c>
       <c r="G28">
-        <v>-5.272028737224556</v>
+        <v>-6.371650862300151</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.622894139659622</v>
       </c>
       <c r="E29">
-        <v>-37.05030667818799</v>
+        <v>-37.07118279491224</v>
       </c>
       <c r="F29">
-        <v>-1.53031283330087</v>
+        <v>-1.169949818795806</v>
       </c>
       <c r="G29">
-        <v>-5.483300632515807</v>
+        <v>-5.81783361218729</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.443589558195917</v>
       </c>
       <c r="E30">
-        <v>-37.19122306183376</v>
+        <v>-36.51440743791705</v>
       </c>
       <c r="F30">
-        <v>-1.861655652583658</v>
+        <v>-0.5886197995939748</v>
       </c>
       <c r="G30">
-        <v>-5.560518625287164</v>
+        <v>-6.412227054735234</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.296891197273639</v>
       </c>
       <c r="E31">
-        <v>-37.29926470123785</v>
+        <v>-36.01984510996213</v>
       </c>
       <c r="F31">
-        <v>-1.797546642546199</v>
+        <v>-1.185658978222496</v>
       </c>
       <c r="G31">
-        <v>-6.939023098330073</v>
+        <v>-6.568884783924987</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.194080771447149</v>
       </c>
       <c r="E32">
-        <v>-36.07034400646072</v>
+        <v>-34.99875526309074</v>
       </c>
       <c r="F32">
-        <v>-1.624747545587416</v>
+        <v>-1.287507578764098</v>
       </c>
       <c r="G32">
-        <v>-6.991642655563961</v>
+        <v>-6.318999976131169</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.136986077316392</v>
       </c>
       <c r="E33">
-        <v>-35.21206419673394</v>
+        <v>-35.1833530468454</v>
       </c>
       <c r="F33">
-        <v>-2.164563104030548</v>
+        <v>-1.32139443247782</v>
       </c>
       <c r="G33">
-        <v>-7.395010527124737</v>
+        <v>-6.530911503847245</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.13370387966407</v>
       </c>
       <c r="E34">
-        <v>-34.87358578018306</v>
+        <v>-34.59708158302128</v>
       </c>
       <c r="F34">
-        <v>-1.748870945590297</v>
+        <v>-1.292034606620397</v>
       </c>
       <c r="G34">
-        <v>-7.269295342828859</v>
+        <v>-5.893174479597637</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.192109387261828</v>
       </c>
       <c r="E35">
-        <v>-33.68255690892801</v>
+        <v>-34.92630664474044</v>
       </c>
       <c r="F35">
-        <v>-2.243812185088974</v>
+        <v>-1.566275575726007</v>
       </c>
       <c r="G35">
-        <v>-6.528279873299402</v>
+        <v>-5.789402603590067</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.312022919429955</v>
       </c>
       <c r="E36">
-        <v>-36.37293244734809</v>
+        <v>-33.79396472611087</v>
       </c>
       <c r="F36">
-        <v>-1.803768510108626</v>
+        <v>-1.775894775371825</v>
       </c>
       <c r="G36">
-        <v>-5.720340576921346</v>
+        <v>-6.120928005492587</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.505098872932493</v>
       </c>
       <c r="E37">
-        <v>-32.94713532000664</v>
+        <v>-34.74247097526388</v>
       </c>
       <c r="F37">
-        <v>-3.15727114423885</v>
+        <v>-2.003453099492669</v>
       </c>
       <c r="G37">
-        <v>-6.335056055366517</v>
+        <v>-5.092607925944886</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.771154121343884</v>
       </c>
       <c r="E38">
-        <v>-33.02532575301353</v>
+        <v>-33.3246269271373</v>
       </c>
       <c r="F38">
-        <v>-2.154052778423827</v>
+        <v>-1.990740144961905</v>
       </c>
       <c r="G38">
-        <v>-6.175617883187228</v>
+        <v>-5.542836052171555</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.113422104236342</v>
       </c>
       <c r="E39">
-        <v>-33.45516651228798</v>
+        <v>-32.49482984067619</v>
       </c>
       <c r="F39">
-        <v>-3.093640102192806</v>
+        <v>-1.821913069699546</v>
       </c>
       <c r="G39">
-        <v>-6.387834868020462</v>
+        <v>-5.55551121716141</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.538751741865639</v>
       </c>
       <c r="E40">
-        <v>-31.89793030907183</v>
+        <v>-32.07983058207101</v>
       </c>
       <c r="F40">
-        <v>-3.032180211109499</v>
+        <v>-2.271348774292834</v>
       </c>
       <c r="G40">
-        <v>-5.457811933072768</v>
+        <v>-5.395731037440685</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.038423790050927</v>
       </c>
       <c r="E41">
-        <v>-31.43576510605624</v>
+        <v>-31.32161201618766</v>
       </c>
       <c r="F41">
-        <v>-2.368796258823363</v>
+        <v>-1.995160313423243</v>
       </c>
       <c r="G41">
-        <v>-4.428904435992067</v>
+        <v>-4.457714002555002</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.619898035023368</v>
       </c>
       <c r="E42">
-        <v>-31.35379525074376</v>
+        <v>-30.81676010717548</v>
       </c>
       <c r="F42">
-        <v>-3.189735691121965</v>
+        <v>-1.985441907053599</v>
       </c>
       <c r="G42">
-        <v>-5.272749302731703</v>
+        <v>-4.566822240506808</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.273951169275244</v>
       </c>
       <c r="E43">
-        <v>-32.02769947352176</v>
+        <v>-31.30190502845135</v>
       </c>
       <c r="F43">
-        <v>-2.521238226858348</v>
+        <v>-2.078851928862883</v>
       </c>
       <c r="G43">
-        <v>-4.947735097839419</v>
+        <v>-4.485009337255091</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.987629083534318</v>
       </c>
       <c r="E44">
-        <v>-30.02638530260965</v>
+        <v>-29.89960229710227</v>
       </c>
       <c r="F44">
-        <v>-2.656238919227389</v>
+        <v>-2.251438963766549</v>
       </c>
       <c r="G44">
-        <v>-4.639967471716029</v>
+        <v>-4.062737064110064</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.750490539642443</v>
       </c>
       <c r="E45">
-        <v>-28.43916914344522</v>
+        <v>-29.18288261877661</v>
       </c>
       <c r="F45">
-        <v>-2.998344716174751</v>
+        <v>-2.519508595721302</v>
       </c>
       <c r="G45">
-        <v>-5.058981535611347</v>
+        <v>-4.249478403223215</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>7.529447524252528</v>
       </c>
       <c r="E46">
-        <v>-28.40047575013746</v>
+        <v>-27.98866823443541</v>
       </c>
       <c r="F46">
-        <v>-2.177025063238263</v>
+        <v>-2.316732539190011</v>
       </c>
       <c r="G46">
-        <v>-4.43308684882703</v>
+        <v>-4.375143983371862</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>8.30959955527843</v>
       </c>
       <c r="E47">
-        <v>-28.48011773050237</v>
+        <v>-29.3393673150735</v>
       </c>
       <c r="F47">
-        <v>-2.179893699554158</v>
+        <v>-2.28788215928531</v>
       </c>
       <c r="G47">
-        <v>-4.097191060478986</v>
+        <v>-4.461162796159862</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>9.063909197455734</v>
       </c>
       <c r="E48">
-        <v>-27.04521229025338</v>
+        <v>-28.63815780444041</v>
       </c>
       <c r="F48">
-        <v>-2.36877472127089</v>
+        <v>-2.321237201126435</v>
       </c>
       <c r="G48">
-        <v>-5.439701197844215</v>
+        <v>-4.16546725302578</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>9.766743816672104</v>
       </c>
       <c r="E49">
-        <v>-27.57231295233267</v>
+        <v>-27.7290219220411</v>
       </c>
       <c r="F49">
-        <v>-2.816885038019699</v>
+        <v>-2.374083727955432</v>
       </c>
       <c r="G49">
-        <v>-4.421978130591843</v>
+        <v>-4.935809216547213</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>10.40400799605705</v>
       </c>
       <c r="E50">
-        <v>-26.61149658481286</v>
+        <v>-25.20497003754643</v>
       </c>
       <c r="F50">
-        <v>-3.338020083162299</v>
+        <v>-2.207468393658548</v>
       </c>
       <c r="G50">
-        <v>-5.805025299223288</v>
+        <v>-3.721909579229406</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>10.94705792602224</v>
       </c>
       <c r="E51">
-        <v>-26.38121762969642</v>
+        <v>-25.6029473595368</v>
       </c>
       <c r="F51">
-        <v>-2.533773910764912</v>
+        <v>-2.559445844945072</v>
       </c>
       <c r="G51">
-        <v>-5.336803921274667</v>
+        <v>-4.288300175293069</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>11.38807352634247</v>
       </c>
       <c r="E52">
-        <v>-26.94732940574982</v>
+        <v>-26.34330296351206</v>
       </c>
       <c r="F52">
-        <v>-2.775415309100751</v>
+        <v>-2.397428778101128</v>
       </c>
       <c r="G52">
-        <v>-6.547829128797658</v>
+        <v>-3.743521322954642</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>11.71104582986283</v>
       </c>
       <c r="E53">
-        <v>-25.72785934334234</v>
+        <v>-25.16957221742491</v>
       </c>
       <c r="F53">
-        <v>-2.799102474983802</v>
+        <v>-2.365808337601465</v>
       </c>
       <c r="G53">
-        <v>-5.411319793394223</v>
+        <v>-4.233565914940379</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>11.90517190345648</v>
       </c>
       <c r="E54">
-        <v>-23.69093346192548</v>
+        <v>-24.30651829128024</v>
       </c>
       <c r="F54">
-        <v>-2.712565417515546</v>
+        <v>-2.966800485476146</v>
       </c>
       <c r="G54">
-        <v>-5.798305242645763</v>
+        <v>-4.768196803053149</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>11.97190112673487</v>
       </c>
       <c r="E55">
-        <v>-23.5529513220807</v>
+        <v>-23.40685380730721</v>
       </c>
       <c r="F55">
-        <v>-2.663933624031993</v>
+        <v>-2.529889696013186</v>
       </c>
       <c r="G55">
-        <v>-6.389176790740295</v>
+        <v>-4.604171552627275</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>11.90233939962248</v>
       </c>
       <c r="E56">
-        <v>-22.96481506637173</v>
+        <v>-22.45386208992338</v>
       </c>
       <c r="F56">
-        <v>-2.761767956139629</v>
+        <v>-2.609540535261969</v>
       </c>
       <c r="G56">
-        <v>-5.78711298058366</v>
+        <v>-4.482098357036</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>11.71095232665083</v>
       </c>
       <c r="E57">
-        <v>-24.12570408304251</v>
+        <v>-22.21608658836562</v>
       </c>
       <c r="F57">
-        <v>-2.8153169385262</v>
+        <v>-2.785222350782494</v>
       </c>
       <c r="G57">
-        <v>-5.558988728956773</v>
+        <v>-5.288416381022974</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>11.40368356348728</v>
       </c>
       <c r="E58">
-        <v>-24.0393878920786</v>
+        <v>-21.64896142874895</v>
       </c>
       <c r="F58">
-        <v>-3.036445474866514</v>
+        <v>-2.746792730231819</v>
       </c>
       <c r="G58">
-        <v>-6.506203417036948</v>
+        <v>-4.872005229484996</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.99438265519693</v>
       </c>
       <c r="E59">
-        <v>-22.82782969724491</v>
+        <v>-20.05382924879941</v>
       </c>
       <c r="F59">
-        <v>-2.007736587332545</v>
+        <v>-2.7707250928661</v>
       </c>
       <c r="G59">
-        <v>-7.369067558122844</v>
+        <v>-5.173791639750145</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.50690204872812</v>
       </c>
       <c r="E60">
-        <v>-20.79719177777384</v>
+        <v>-21.07507068788415</v>
       </c>
       <c r="F60">
-        <v>-2.126840909241864</v>
+        <v>-2.683160031450969</v>
       </c>
       <c r="G60">
-        <v>-7.089005153600349</v>
+        <v>-5.840257297480362</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>9.951264759409058</v>
       </c>
       <c r="E61">
-        <v>-21.85419236636536</v>
+        <v>-19.82489593415221</v>
       </c>
       <c r="F61">
-        <v>-2.634090031611335</v>
+        <v>-2.670606123461543</v>
       </c>
       <c r="G61">
-        <v>-7.677816824212493</v>
+        <v>-5.742163790958463</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.361656705846942</v>
       </c>
       <c r="E62">
-        <v>-21.46091232638337</v>
+        <v>-19.70325668087063</v>
       </c>
       <c r="F62">
-        <v>-3.525708255819</v>
+        <v>-2.858963616979706</v>
       </c>
       <c r="G62">
-        <v>-7.355820640067535</v>
+        <v>-6.426599203709313</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>8.756680766067204</v>
       </c>
       <c r="E63">
-        <v>-20.28866427673919</v>
+        <v>-19.08909640300029</v>
       </c>
       <c r="F63">
-        <v>-3.403823104538484</v>
+        <v>-2.830547301594072</v>
       </c>
       <c r="G63">
-        <v>-7.511201715152234</v>
+        <v>-6.440211626007377</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.160613265744903</v>
       </c>
       <c r="E64">
-        <v>-20.94498380276787</v>
+        <v>-19.12341023496602</v>
       </c>
       <c r="F64">
-        <v>-3.25563645985168</v>
+        <v>-2.806165135460071</v>
       </c>
       <c r="G64">
-        <v>-7.366926747558131</v>
+        <v>-6.872488272425551</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>7.604599830017084</v>
       </c>
       <c r="E65">
-        <v>-19.96154489316172</v>
+        <v>-18.11297129853716</v>
       </c>
       <c r="F65">
-        <v>-2.644658342936252</v>
+        <v>-2.911741389314271</v>
       </c>
       <c r="G65">
-        <v>-8.220172905570367</v>
+        <v>-7.167531129411854</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>7.09871939179741</v>
       </c>
       <c r="E66">
-        <v>-19.38539065212488</v>
+        <v>-17.24780338782815</v>
       </c>
       <c r="F66">
-        <v>-3.441982677315846</v>
+        <v>-3.366137357915523</v>
       </c>
       <c r="G66">
-        <v>-6.803572447453933</v>
+        <v>-6.781336735771421</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>6.674679927442074</v>
       </c>
       <c r="E67">
-        <v>-19.57139222130732</v>
+        <v>-17.5808577103888</v>
       </c>
       <c r="F67">
-        <v>-3.040410041256312</v>
+        <v>-3.149316332069766</v>
       </c>
       <c r="G67">
-        <v>-8.422800625520441</v>
+        <v>-7.463842808269439</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>6.343380754332853</v>
       </c>
       <c r="E68">
-        <v>-20.34782677206137</v>
+        <v>-17.54344973598607</v>
       </c>
       <c r="F68">
-        <v>-3.103211059164751</v>
+        <v>-3.470196042687794</v>
       </c>
       <c r="G68">
-        <v>-8.993760024618553</v>
+        <v>-7.529949472061018</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.112652621686507</v>
       </c>
       <c r="E69">
-        <v>-19.42346729355091</v>
+        <v>-18.44617098349418</v>
       </c>
       <c r="F69">
-        <v>-3.186818181129305</v>
+        <v>-3.236769563885519</v>
       </c>
       <c r="G69">
-        <v>-8.955703200713895</v>
+        <v>-7.539953845334165</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>5.997357822218675</v>
       </c>
       <c r="E70">
-        <v>-19.35695361418378</v>
+        <v>-17.66616051778945</v>
       </c>
       <c r="F70">
-        <v>-3.690178946910036</v>
+        <v>-3.588212718197237</v>
       </c>
       <c r="G70">
-        <v>-8.383532416125508</v>
+        <v>-7.682761574468062</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>5.986330510931898</v>
       </c>
       <c r="E71">
-        <v>-20.3326260186125</v>
+        <v>-17.97641786338812</v>
       </c>
       <c r="F71">
-        <v>-3.333964396358193</v>
+        <v>-3.613079479261875</v>
       </c>
       <c r="G71">
-        <v>-8.263653551363063</v>
+        <v>-7.72406747001636</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>6.085246333967495</v>
       </c>
       <c r="E72">
-        <v>-19.56496305017649</v>
+        <v>-18.41787930794944</v>
       </c>
       <c r="F72">
-        <v>-4.709009553165621</v>
+        <v>-3.737373522949732</v>
       </c>
       <c r="G72">
-        <v>-8.115437664808676</v>
+        <v>-7.269773109089033</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>6.283375418052934</v>
       </c>
       <c r="E73">
-        <v>-20.79021438274813</v>
+        <v>-18.28542924558934</v>
       </c>
       <c r="F73">
-        <v>-3.463734776945958</v>
+        <v>-3.897401679659555</v>
       </c>
       <c r="G73">
-        <v>-7.393386643989064</v>
+        <v>-7.223108660267474</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>6.561938708092686</v>
       </c>
       <c r="E74">
-        <v>-20.11575778286393</v>
+        <v>-18.09965194981843</v>
       </c>
       <c r="F74">
-        <v>-3.928126654996791</v>
+        <v>-4.15045798080597</v>
       </c>
       <c r="G74">
-        <v>-7.183130328343756</v>
+        <v>-7.044102957377792</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>6.916440330641518</v>
       </c>
       <c r="E75">
-        <v>-20.09868393110755</v>
+        <v>-18.14430727798299</v>
       </c>
       <c r="F75">
-        <v>-3.446760700495193</v>
+        <v>-3.967336597640903</v>
       </c>
       <c r="G75">
-        <v>-7.432667907106955</v>
+        <v>-7.078191449503958</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>7.321152689493264</v>
       </c>
       <c r="E76">
-        <v>-19.21367612989984</v>
+        <v>-18.37471913586183</v>
       </c>
       <c r="F76">
-        <v>-4.714133833919338</v>
+        <v>-3.996567198183489</v>
       </c>
       <c r="G76">
-        <v>-7.675469764825082</v>
+        <v>-7.485086437007328</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>7.767068347981076</v>
       </c>
       <c r="E77">
-        <v>-19.83762968007413</v>
+        <v>-18.71823955096104</v>
       </c>
       <c r="F77">
-        <v>-4.252435806662409</v>
+        <v>-3.950572098143047</v>
       </c>
       <c r="G77">
-        <v>-7.059025973460595</v>
+        <v>-6.690618582719417</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>8.241527896290242</v>
       </c>
       <c r="E78">
-        <v>-21.73465463801414</v>
+        <v>-20.12636923779886</v>
       </c>
       <c r="F78">
-        <v>-4.32308477734497</v>
+        <v>-4.606583580544267</v>
       </c>
       <c r="G78">
-        <v>-7.07181862195705</v>
+        <v>-6.11476664825756</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>8.722788364971942</v>
       </c>
       <c r="E79">
-        <v>-20.94100502631868</v>
+        <v>-19.29291109555492</v>
       </c>
       <c r="F79">
-        <v>-4.744355161875673</v>
+        <v>-4.09814326584957</v>
       </c>
       <c r="G79">
-        <v>-6.080795639637993</v>
+        <v>-5.345348888321381</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>9.211456784751626</v>
       </c>
       <c r="E80">
-        <v>-21.98758936090753</v>
+        <v>-20.20950822209928</v>
       </c>
       <c r="F80">
-        <v>-4.533474358675392</v>
+        <v>-4.551811099503762</v>
       </c>
       <c r="G80">
-        <v>-6.840083710560653</v>
+        <v>-5.200815457012759</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>9.690270448529596</v>
       </c>
       <c r="E81">
-        <v>-22.37972726777519</v>
+        <v>-20.6656388090599</v>
       </c>
       <c r="F81">
-        <v>-5.227718310185421</v>
+        <v>-4.533977177688891</v>
       </c>
       <c r="G81">
-        <v>-5.567995797796113</v>
+        <v>-5.111467944871088</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>10.15690894380397</v>
       </c>
       <c r="E82">
-        <v>-22.93395670622826</v>
+        <v>-23.0891123749012</v>
       </c>
       <c r="F82">
-        <v>-5.1424047513711</v>
+        <v>-4.120948220448641</v>
       </c>
       <c r="G82">
-        <v>-6.675173417718391</v>
+        <v>-5.15077531543489</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>10.61097619852344</v>
       </c>
       <c r="E83">
-        <v>-24.405605607068</v>
+        <v>-22.89003649646819</v>
       </c>
       <c r="F83">
-        <v>-4.385349013176396</v>
+        <v>-4.366742224574713</v>
       </c>
       <c r="G83">
-        <v>-4.97020316579054</v>
+        <v>-4.805021355510802</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>11.03789751172836</v>
       </c>
       <c r="E84">
-        <v>-23.73792704806592</v>
+        <v>-24.42028720910127</v>
       </c>
       <c r="F84">
-        <v>-4.113272568094301</v>
+        <v>-4.448628827443653</v>
       </c>
       <c r="G84">
-        <v>-5.361431075002639</v>
+        <v>-4.834397453650009</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>11.44557665040884</v>
       </c>
       <c r="E85">
-        <v>-26.55971019280357</v>
+        <v>-23.86775228086873</v>
       </c>
       <c r="F85">
-        <v>-4.467244728086766</v>
+        <v>-4.439104259046264</v>
       </c>
       <c r="G85">
-        <v>-5.386909331467313</v>
+        <v>-4.25547006205982</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>11.82016947360102</v>
       </c>
       <c r="E86">
-        <v>-27.56752429967514</v>
+        <v>-26.76008602638125</v>
       </c>
       <c r="F86">
-        <v>-5.410353441685045</v>
+        <v>-4.717040575135762</v>
       </c>
       <c r="G86">
-        <v>-6.193167308328691</v>
+        <v>-3.902210211436281</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>12.15787204305671</v>
       </c>
       <c r="E87">
-        <v>-27.63187000273071</v>
+        <v>-27.34894494086074</v>
       </c>
       <c r="F87">
-        <v>-4.236002654125673</v>
+        <v>-5.007861317808405</v>
       </c>
       <c r="G87">
-        <v>-4.410365538650571</v>
+        <v>-3.809847289291875</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>12.45414635587372</v>
       </c>
       <c r="E88">
-        <v>-29.60766891986874</v>
+        <v>-29.17115810320661</v>
       </c>
       <c r="F88">
-        <v>-4.91491269664248</v>
+        <v>-4.483438482444093</v>
       </c>
       <c r="G88">
-        <v>-5.309458982427347</v>
+        <v>-4.096929986019875</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>12.68779651365467</v>
       </c>
       <c r="E89">
-        <v>-32.7371551852403</v>
+        <v>-29.05982712043326</v>
       </c>
       <c r="F89">
-        <v>-4.440191077078737</v>
+        <v>-4.460848903369751</v>
       </c>
       <c r="G89">
-        <v>-4.502514379738506</v>
+        <v>-4.094507215039322</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>12.85839101259907</v>
       </c>
       <c r="E90">
-        <v>-31.54864523665375</v>
+        <v>-30.79221047503442</v>
       </c>
       <c r="F90">
-        <v>-4.915695503838125</v>
+        <v>-4.555816255896297</v>
       </c>
       <c r="G90">
-        <v>-4.842668292514656</v>
+        <v>-4.365003851379978</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>12.94458878493181</v>
       </c>
       <c r="E91">
-        <v>-34.55060507169078</v>
+        <v>-32.08484143153441</v>
       </c>
       <c r="F91">
-        <v>-4.573240135846782</v>
+        <v>-4.336969871750695</v>
       </c>
       <c r="G91">
-        <v>-4.119993303737769</v>
+        <v>-4.256490863194945</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>12.93818278639462</v>
       </c>
       <c r="E92">
-        <v>-34.86912107800887</v>
+        <v>-34.67144483179234</v>
       </c>
       <c r="F92">
-        <v>-4.573614557912848</v>
+        <v>-3.925900831785469</v>
       </c>
       <c r="G92">
-        <v>-5.246720179158303</v>
+        <v>-4.579586170812761</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>12.83112128387474</v>
       </c>
       <c r="E93">
-        <v>-36.50712685846462</v>
+        <v>-36.04878260986787</v>
       </c>
       <c r="F93">
-        <v>-3.983931281821186</v>
+        <v>-4.280008015664591</v>
       </c>
       <c r="G93">
-        <v>-5.549689256723227</v>
+        <v>-4.818563287704906</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>12.60564379362907</v>
       </c>
       <c r="E94">
-        <v>-38.83661325202505</v>
+        <v>-37.70003090463284</v>
       </c>
       <c r="F94">
-        <v>-4.650588942083186</v>
+        <v>-3.826822291838829</v>
       </c>
       <c r="G94">
-        <v>-5.319238831665657</v>
+        <v>-6.031455177610543</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>12.27198406490027</v>
       </c>
       <c r="E95">
-        <v>-41.50333002213326</v>
+        <v>-39.63016111004305</v>
       </c>
       <c r="F95">
-        <v>-4.190722435153845</v>
+        <v>-3.844925433059609</v>
       </c>
       <c r="G95">
-        <v>-6.324114424785161</v>
+        <v>-6.0264738769307</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>11.81181396473404</v>
       </c>
       <c r="E96">
-        <v>-43.00204747778257</v>
+        <v>-42.18575455794414</v>
       </c>
       <c r="F96">
-        <v>-4.408624480460256</v>
+        <v>-3.720314124656479</v>
       </c>
       <c r="G96">
-        <v>-6.826669704851513</v>
+        <v>-6.330424594461881</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>11.24521871162154</v>
       </c>
       <c r="E97">
-        <v>-43.45152046698949</v>
+        <v>-43.51647876871547</v>
       </c>
       <c r="F97">
-        <v>-4.84620541915208</v>
+        <v>-3.63567568527544</v>
       </c>
       <c r="G97">
-        <v>-7.238146549112287</v>
+        <v>-6.82134117514105</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>10.55565261420426</v>
       </c>
       <c r="E98">
-        <v>-46.1448447854502</v>
+        <v>-45.01034112032606</v>
       </c>
       <c r="F98">
-        <v>-4.193873544754095</v>
+        <v>-3.435566971781163</v>
       </c>
       <c r="G98">
-        <v>-7.218623401059942</v>
+        <v>-6.539404256002135</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>9.779452347704751</v>
       </c>
       <c r="E99">
-        <v>-47.64352174728909</v>
+        <v>-47.14781105640286</v>
       </c>
       <c r="F99">
-        <v>-4.623235422075343</v>
+        <v>-3.166227452597918</v>
       </c>
       <c r="G99">
-        <v>-7.573107690896713</v>
+        <v>-8.613381064554826</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>8.878552830483576</v>
       </c>
       <c r="E100">
-        <v>-50.17150983781688</v>
+        <v>-49.34650244231613</v>
       </c>
       <c r="F100">
-        <v>-4.417730723319231</v>
+        <v>-3.112772075727863</v>
       </c>
       <c r="G100">
-        <v>-7.494224043076224</v>
+        <v>-7.481739462441521</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.954788316060801</v>
       </c>
       <c r="E101">
-        <v>-50.87568577963872</v>
+        <v>-51.83268949916234</v>
       </c>
       <c r="F101">
-        <v>-4.217264983474347</v>
+        <v>-2.443470266716127</v>
       </c>
       <c r="G101">
-        <v>-8.618227911888226</v>
+        <v>-8.542398835239341</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.860042634362373</v>
       </c>
       <c r="E102">
-        <v>-52.68650149180644</v>
+        <v>-53.75376674218727</v>
       </c>
       <c r="F102">
-        <v>-3.883871954869631</v>
+        <v>-2.627045595217928</v>
       </c>
       <c r="G102">
-        <v>-7.667431282229044</v>
+        <v>-8.838663520694286</v>
       </c>
     </row>
   </sheetData>
